--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1907.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1907.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CE3EC3-C30C-412A-921A-08A19163B8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FCD437-601A-4F43-B76F-EB2978D3DEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{26DDFB96-2A59-463B-8827-7F297B6E5252}"/>
+    <workbookView xWindow="58470" yWindow="90" windowWidth="34560" windowHeight="20130" xr2:uid="{26DDFB96-2A59-463B-8827-7F297B6E5252}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -467,7 +467,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,6 +486,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -499,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -516,6 +522,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,9 +544,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -574,7 +584,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -680,7 +690,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -822,7 +832,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7803,15 +7813,15 @@
         <v>0</v>
       </c>
       <c r="AE67" s="7">
-        <f t="shared" ref="AE67:AE122" si="15">B67-H67-T67</f>
+        <f t="shared" ref="AE67:AE107" si="15">B67-H67-T67</f>
         <v>0</v>
       </c>
       <c r="AF67" s="7">
-        <f t="shared" ref="AF67:AF122" si="16">C67-L67-X67</f>
+        <f t="shared" ref="AF67:AF107" si="16">C67-L67-X67</f>
         <v>0</v>
       </c>
       <c r="AG67" s="7">
-        <f t="shared" ref="AG67:AG122" si="17">D67-P67-AB67</f>
+        <f t="shared" ref="AG67:AG107" si="17">D67-P67-AB67</f>
         <v>0</v>
       </c>
     </row>
@@ -9486,8 +9496,8 @@
       <c r="B84" s="2">
         <v>855067</v>
       </c>
-      <c r="C84" s="2">
-        <v>36595</v>
+      <c r="C84" s="11">
+        <v>33595</v>
       </c>
       <c r="D84" s="2">
         <v>21862</v>
@@ -9544,14 +9554,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="V84" s="3">
-        <v>18626</v>
+      <c r="V84" s="10">
+        <v>15626</v>
       </c>
       <c r="W84" s="3">
         <v>13930</v>
       </c>
-      <c r="X84" s="3">
-        <v>32556</v>
+      <c r="X84" s="10">
+        <v>29556</v>
       </c>
       <c r="Y84" s="5">
         <f t="shared" si="13"/>
@@ -12360,4 +12370,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>